--- a/data/trans_dic/P33_1_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P33_1_R-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que duerme las horas de sueño recomendadas por la Sociedad Española del Sueño</t>
+          <t>Población que duerme las horas de sueño recomendadas por la Sociedad Española del Sueño (tasa de respuesta: 98,8%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>86,56; 92,3</t>
+          <t>86,66; 92,43</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>80,44; 87,16</t>
+          <t>80,46; 87,26</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>79,19; 86,9</t>
+          <t>79,71; 87,14</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>84,45; 95,41</t>
+          <t>83,93; 95,57</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>84,62; 90,67</t>
+          <t>84,76; 90,65</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73,31; 81,54</t>
+          <t>72,61; 81,09</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>76,74; 84,54</t>
+          <t>77,0; 84,95</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>79,03; 89,71</t>
+          <t>78,98; 89,78</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>86,51; 90,62</t>
+          <t>86,69; 90,69</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>78,39; 83,56</t>
+          <t>77,99; 83,46</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>79,63; 85,16</t>
+          <t>79,83; 85,2</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>84,36; 91,86</t>
+          <t>83,87; 91,66</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>85,19; 90,34</t>
+          <t>85,14; 90,39</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>77,21; 83,32</t>
+          <t>77,34; 83,66</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>78,87; 85,2</t>
+          <t>78,84; 85,42</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>78,98; 88,67</t>
+          <t>79,38; 88,7</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>81,46; 87,21</t>
+          <t>81,54; 87,56</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>75,86; 82,58</t>
+          <t>75,78; 82,43</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>81,28; 87,19</t>
+          <t>81,57; 87,45</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>77,14; 89,09</t>
+          <t>77,09; 89,37</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>84,42; 88,1</t>
+          <t>84,21; 88,22</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>77,5; 82,19</t>
+          <t>77,7; 82,27</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>81,06; 85,44</t>
+          <t>81,08; 85,51</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>79,92; 87,15</t>
+          <t>79,81; 87,01</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>80,59; 86,69</t>
+          <t>80,79; 86,76</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>75,29; 81,84</t>
+          <t>75,22; 81,75</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>77,06; 83,56</t>
+          <t>76,97; 83,53</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>75,78; 83,15</t>
+          <t>76,21; 83,42</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>80,45; 86,13</t>
+          <t>80,1; 85,89</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>73,78; 80,67</t>
+          <t>73,92; 80,62</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>75,99; 82,27</t>
+          <t>75,6; 81,88</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>74,2; 79,92</t>
+          <t>73,84; 79,81</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>81,48; 85,57</t>
+          <t>81,12; 85,43</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>75,27; 79,98</t>
+          <t>75,71; 80,14</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>77,41; 81,89</t>
+          <t>77,39; 81,77</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>75,83; 80,5</t>
+          <t>75,8; 80,46</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>79,09; 85,99</t>
+          <t>78,78; 86,03</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>69,7; 77,06</t>
+          <t>69,52; 77,04</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>76,0; 82,29</t>
+          <t>75,83; 82,72</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>70,02; 90,61</t>
+          <t>70,2; 90,34</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>75,45; 82,5</t>
+          <t>75,14; 82,15</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>62,76; 70,77</t>
+          <t>62,7; 71,03</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>68,48; 76,01</t>
+          <t>68,73; 75,84</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>69,89; 77,31</t>
+          <t>69,94; 77,55</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>78,07; 83,07</t>
+          <t>78,04; 83,25</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>67,41; 72,76</t>
+          <t>67,28; 72,87</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>73,39; 78,47</t>
+          <t>73,23; 78,44</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>71,25; 86,27</t>
+          <t>71,4; 86,32</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>74,56; 82,75</t>
+          <t>74,48; 82,81</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>69,22; 77,94</t>
+          <t>68,95; 77,71</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>71,09; 79,31</t>
+          <t>70,6; 79,2</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>67,2; 74,61</t>
+          <t>66,77; 74,49</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>68,71; 77,56</t>
+          <t>68,78; 77,06</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>54,53; 63,9</t>
+          <t>54,08; 63,97</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>61,08; 69,99</t>
+          <t>60,52; 69,33</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>57,9; 64,25</t>
+          <t>58,06; 64,17</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>73,05; 79,13</t>
+          <t>72,9; 78,95</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>62,88; 69,53</t>
+          <t>62,67; 69,12</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>67,28; 73,28</t>
+          <t>67,26; 73,44</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>63,56; 68,58</t>
+          <t>63,44; 68,36</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>58,82; 69,98</t>
+          <t>58,49; 69,81</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>47,88; 60,28</t>
+          <t>47,93; 60,2</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>58,05; 68,79</t>
+          <t>57,98; 68,67</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>60,93; 69,39</t>
+          <t>61,34; 69,13</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>51,81; 61,51</t>
+          <t>51,5; 61,48</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>48,3; 58,83</t>
+          <t>47,94; 58,26</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>48,27; 58,52</t>
+          <t>47,46; 58,19</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>15,42; 60,58</t>
+          <t>16,26; 60,6</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>56,04; 63,79</t>
+          <t>56,42; 63,98</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>49,98; 57,76</t>
+          <t>49,69; 57,78</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>54,05; 61,93</t>
+          <t>53,99; 61,29</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>25,78; 63,0</t>
+          <t>23,86; 63,07</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>51,33; 65,04</t>
+          <t>51,59; 64,64</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>45,77; 59,52</t>
+          <t>45,92; 59,56</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>51,59; 62,72</t>
+          <t>51,37; 62,76</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>55,3; 64,69</t>
+          <t>55,24; 65,07</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>41,03; 52,5</t>
+          <t>40,66; 52,53</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>38,66; 49,27</t>
+          <t>38,17; 48,27</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>47,62; 59,37</t>
+          <t>48,42; 59,52</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>47,78; 54,76</t>
+          <t>47,93; 55,01</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>46,79; 54,92</t>
+          <t>46,59; 55,6</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>43,39; 51,43</t>
+          <t>43,29; 51,03</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>51,11; 59,57</t>
+          <t>51,39; 59,84</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>52,52; 58,08</t>
+          <t>52,24; 57,74</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>80,16; 82,8</t>
+          <t>79,98; 82,81</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>72,57; 75,59</t>
+          <t>72,41; 75,62</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>75,34; 78,3</t>
+          <t>75,35; 78,49</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>74,57; 82,57</t>
+          <t>74,27; 82,34</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>74,51; 77,4</t>
+          <t>74,42; 77,33</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>65,95; 69,24</t>
+          <t>65,63; 69,03</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>69,93; 73,14</t>
+          <t>69,9; 73,04</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>53,85; 70,67</t>
+          <t>53,22; 70,55</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>77,7; 79,69</t>
+          <t>77,61; 79,61</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>69,55; 71,84</t>
+          <t>69,68; 71,95</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>73,05; 75,15</t>
+          <t>72,94; 75,15</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>64,96; 74,31</t>
+          <t>64,36; 74,58</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que duerme las horas de sueño recomendadas por la Sociedad Española del Sueño</t>
+          <t>Población que duerme las horas de sueño recomendadas por la Sociedad Española del Sueño (tasa de respuesta: 98,8%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>422112; 450148</t>
+          <t>422614; 450755</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>363795; 394144</t>
+          <t>363861; 394596</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>332163; 364531</t>
+          <t>334356; 365505</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>313479; 354166</t>
+          <t>311555; 354753</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>393231; 421314</t>
+          <t>393859; 421215</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>314690; 350042</t>
+          <t>311699; 348086</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>302982; 333762</t>
+          <t>304005; 335401</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>241867; 274563</t>
+          <t>241732; 274793</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>823875; 863068</t>
+          <t>825652; 863724</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>691044; 736609</t>
+          <t>687494; 735656</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>648364; 693437</t>
+          <t>650060; 693758</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>571299; 622130</t>
+          <t>567977; 620733</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>618707; 656079</t>
+          <t>618367; 656484</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>529782; 571699</t>
+          <t>530684; 574067</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>465725; 503090</t>
+          <t>465576; 504373</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>321214; 360649</t>
+          <t>322841; 360768</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>505808; 541507</t>
+          <t>506296; 543707</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>462125; 503096</t>
+          <t>461622; 502185</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>456579; 489746</t>
+          <t>458181; 491238</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>386819; 446738</t>
+          <t>386558; 448141</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1137253; 1186900</t>
+          <t>1134480; 1188507</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1003942; 1064643</t>
+          <t>1006439; 1065673</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>934037; 984426</t>
+          <t>934236; 985284</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>725814; 791519</t>
+          <t>724802; 790211</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>504439; 542621</t>
+          <t>505689; 543117</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>511266; 555730</t>
+          <t>510735; 555102</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>514384; 557770</t>
+          <t>513782; 557587</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>396586; 435154</t>
+          <t>398799; 436558</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>552618; 591603</t>
+          <t>550203; 589965</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>522997; 571869</t>
+          <t>524042; 571482</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>502568; 544141</t>
+          <t>499987; 541563</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>386507; 416300</t>
+          <t>384634; 415708</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1069735; 1123432</t>
+          <t>1064975; 1121526</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1044621; 1110006</t>
+          <t>1050754; 1112250</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1028673; 1088223</t>
+          <t>1028403; 1086583</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>791850; 840638</t>
+          <t>791464; 840203</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>405194; 440569</t>
+          <t>403639; 440740</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>426965; 472030</t>
+          <t>425871; 471898</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>489309; 529762</t>
+          <t>488161; 532531</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>611454; 791335</t>
+          <t>613099; 788956</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>386758; 422892</t>
+          <t>385168; 421072</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>386734; 436070</t>
+          <t>386336; 437672</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>442390; 491062</t>
+          <t>444006; 489949</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>488576; 540503</t>
+          <t>488926; 542136</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>800126; 851420</t>
+          <t>799852; 853283</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>828310; 893992</t>
+          <t>826755; 895361</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>946643; 1012055</t>
+          <t>944499; 1011672</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1120309; 1356485</t>
+          <t>1122736; 1357326</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>284258; 315492</t>
+          <t>283958; 315716</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>295643; 332846</t>
+          <t>294484; 331895</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>338893; 378102</t>
+          <t>336579; 377577</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>366902; 407369</t>
+          <t>364516; 406708</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>275451; 310900</t>
+          <t>275733; 308913</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>243048; 284847</t>
+          <t>241050; 285157</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>302852; 347025</t>
+          <t>300060; 343744</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>305420; 338931</t>
+          <t>306259; 338506</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>571341; 618851</t>
+          <t>570188; 617470</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>548872; 606856</t>
+          <t>547028; 603289</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>654318; 712700</t>
+          <t>654130; 714186</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>682287; 736151</t>
+          <t>681002; 733836</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>170432; 202779</t>
+          <t>169489; 202284</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>148331; 186753</t>
+          <t>148467; 186496</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>194064; 229988</t>
+          <t>193858; 229593</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>221146; 251859</t>
+          <t>222630; 250919</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>175219; 208041</t>
+          <t>174179; 207936</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>170553; 207715</t>
+          <t>169285; 205703</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>181864; 220501</t>
+          <t>178822; 219273</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>92320; 362804</t>
+          <t>97401; 362905</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>351893; 400593</t>
+          <t>354276; 401748</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>331281; 382883</t>
+          <t>329422; 383032</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>384376; 440406</t>
+          <t>383930; 435854</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>247987; 605990</t>
+          <t>229538; 606624</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>105913; 134202</t>
+          <t>106453; 133388</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>112935; 146857</t>
+          <t>113307; 146950</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>131694; 160114</t>
+          <t>131126; 160204</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>151200; 176874</t>
+          <t>151020; 177909</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>136632; 174820</t>
+          <t>135407; 174910</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>149442; 190445</t>
+          <t>147535; 186585</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>187381; 233596</t>
+          <t>190540; 234184</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>193305; 221538</t>
+          <t>193897; 222548</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>252335; 296231</t>
+          <t>251270; 299894</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>274808; 325670</t>
+          <t>274114; 323152</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>331610; 386470</t>
+          <t>333382; 388199</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>356086; 393791</t>
+          <t>354158; 391495</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>2588708; 2674029</t>
+          <t>2582930; 2674378</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2477335; 2580460</t>
+          <t>2471615; 2581173</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2552237; 2652505</t>
+          <t>2552675; 2658807</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2503236; 2771638</t>
+          <t>2493003; 2764034</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>2501367; 2598566</t>
+          <t>2498276; 2596209</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2340558; 2457196</t>
+          <t>2329295; 2449801</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2468587; 2581803</t>
+          <t>2467351; 2578401</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>1916101; 2514675</t>
+          <t>1893941; 2510660</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>5118185; 5248700</t>
+          <t>5112156; 5243770</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>4842118; 5001553</t>
+          <t>4851463; 5009745</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>5053561; 5198847</t>
+          <t>5045986; 5198786</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>4492493; 5138820</t>
+          <t>4450941; 5157772</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P33_1_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P33_1_R-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>91,01%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>84,99%</t>
+          <t>83,54%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>88,29%</t>
+          <t>87,52%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>86,66; 92,43</t>
+          <t>86,31; 92,24</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>80,46; 87,26</t>
+          <t>80,89; 87,36</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>79,71; 87,14</t>
+          <t>79,44; 87,01</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>83,93; 95,57</t>
+          <t>85,53; 95,35</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>84,76; 90,65</t>
+          <t>84,69; 90,36</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>72,61; 81,09</t>
+          <t>72,94; 81,19</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>77,0; 84,95</t>
+          <t>77,07; 85,03</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>78,98; 89,78</t>
+          <t>77,79; 88,39</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>86,69; 90,69</t>
+          <t>86,51; 90,65</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>77,99; 83,46</t>
+          <t>78,24; 83,26</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>79,83; 85,2</t>
+          <t>79,73; 84,87</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>83,87; 91,66</t>
+          <t>83,79; 90,89</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>84,31%</t>
+          <t>85,47%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>82,11%</t>
+          <t>80,29%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>83,1%</t>
+          <t>82,8%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>85,14; 90,39</t>
+          <t>85,34; 90,3</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>77,34; 83,66</t>
+          <t>77,43; 83,39</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>78,84; 85,42</t>
+          <t>78,86; 85,33</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>79,38; 88,7</t>
+          <t>80,89; 89,11</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>81,54; 87,56</t>
+          <t>81,71; 87,27</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>75,78; 82,43</t>
+          <t>75,77; 82,48</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>81,57; 87,45</t>
+          <t>81,27; 87,3</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>77,09; 89,37</t>
+          <t>76,04; 83,84</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>84,21; 88,22</t>
+          <t>84,35; 88,14</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>77,7; 82,27</t>
+          <t>77,02; 82,02</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>81,08; 85,51</t>
+          <t>81,09; 85,48</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>79,81; 87,01</t>
+          <t>79,32; 85,34</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>79,61%</t>
+          <t>80,24%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>77,01%</t>
+          <t>76,69%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>78,32%</t>
+          <t>78,48%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>80,79; 86,76</t>
+          <t>80,5; 86,53</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>75,22; 81,75</t>
+          <t>75,04; 82,03</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>76,97; 83,53</t>
+          <t>77,38; 83,49</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>76,21; 83,42</t>
+          <t>76,59; 83,41</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>80,1; 85,89</t>
+          <t>80,19; 86,08</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>73,92; 80,62</t>
+          <t>73,67; 80,4</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>75,6; 81,88</t>
+          <t>75,97; 82,06</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>73,84; 79,81</t>
+          <t>73,69; 79,51</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>81,12; 85,43</t>
+          <t>81,39; 85,39</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>75,71; 80,14</t>
+          <t>75,69; 80,17</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>77,39; 81,77</t>
+          <t>77,47; 81,93</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>75,8; 80,46</t>
+          <t>76,16; 80,74</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>79,58%</t>
+          <t>72,2%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>72,93%</t>
+          <t>71,47%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>76,63%</t>
+          <t>71,83%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>78,78; 86,03</t>
+          <t>79,1; 86,2</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>69,52; 77,04</t>
+          <t>69,58; 77,41</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>75,83; 82,72</t>
+          <t>75,72; 82,36</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>70,2; 90,34</t>
+          <t>68,29; 75,77</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>75,14; 82,15</t>
+          <t>74,93; 82,5</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>62,7; 71,03</t>
+          <t>62,77; 70,76</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>68,73; 75,84</t>
+          <t>68,92; 76,23</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>69,94; 77,55</t>
+          <t>68,88; 73,93</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>78,04; 83,25</t>
+          <t>78,08; 83,4</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>67,28; 72,87</t>
+          <t>67,2; 72,81</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>73,23; 78,44</t>
+          <t>73,22; 78,18</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>71,4; 86,32</t>
+          <t>69,62; 74,24</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>71,04%</t>
+          <t>71,02%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>61,03%</t>
+          <t>61,21%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>66,12%</t>
+          <t>66,14%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>74,48; 82,81</t>
+          <t>74,52; 82,65</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>68,95; 77,71</t>
+          <t>69,04; 78,04</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>70,6; 79,2</t>
+          <t>71,05; 79,5</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>66,77; 74,49</t>
+          <t>67,31; 74,34</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>68,78; 77,06</t>
+          <t>69,08; 77,37</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>54,08; 63,97</t>
+          <t>53,95; 63,92</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>60,52; 69,33</t>
+          <t>60,63; 69,47</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>58,06; 64,17</t>
+          <t>58,23; 64,29</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>72,9; 78,95</t>
+          <t>73,13; 79,01</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>62,67; 69,12</t>
+          <t>62,83; 69,37</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>67,26; 73,44</t>
+          <t>67,14; 73,37</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>63,44; 68,36</t>
+          <t>63,71; 68,64</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>65,24%</t>
+          <t>65,08%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>39,16%</t>
+          <t>59,83%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>49,0%</t>
+          <t>62,36%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>58,49; 69,81</t>
+          <t>58,39; 69,3</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>47,93; 60,2</t>
+          <t>48,39; 60,29</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>57,98; 68,67</t>
+          <t>57,94; 68,67</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>61,34; 69,13</t>
+          <t>61,24; 68,91</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>51,5; 61,48</t>
+          <t>51,6; 61,78</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>47,94; 58,26</t>
+          <t>48,77; 58,7</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>47,46; 58,19</t>
+          <t>47,62; 58,0</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>16,26; 60,6</t>
+          <t>56,32; 62,93</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>56,42; 63,98</t>
+          <t>56,63; 64,16</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>49,69; 57,78</t>
+          <t>49,63; 57,54</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>53,99; 61,29</t>
+          <t>54,17; 61,59</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>23,86; 63,07</t>
+          <t>59,77; 64,78</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>60,41%</t>
+          <t>60,73%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>51,44%</t>
+          <t>51,97%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>55,06%</t>
+          <t>55,51%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>51,59; 64,64</t>
+          <t>50,81; 64,16</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>45,92; 59,56</t>
+          <t>45,7; 59,33</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>51,37; 62,76</t>
+          <t>51,82; 63,07</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>55,24; 65,07</t>
+          <t>56,34; 65,24</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>40,66; 52,53</t>
+          <t>40,41; 52,44</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>38,17; 48,27</t>
+          <t>38,7; 48,84</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>48,42; 59,52</t>
+          <t>48,2; 59,97</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>47,93; 55,01</t>
+          <t>48,46; 55,4</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>46,59; 55,6</t>
+          <t>46,12; 55,19</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>43,29; 51,03</t>
+          <t>42,83; 51,52</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>51,39; 59,84</t>
+          <t>51,25; 59,31</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>52,24; 57,74</t>
+          <t>52,79; 58,19</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>76,92%</t>
+          <t>75,49%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>65,97%</t>
+          <t>69,28%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>71,29%</t>
+          <t>72,3%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>79,98; 82,81</t>
+          <t>79,88; 82,84</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>72,41; 75,62</t>
+          <t>72,61; 75,79</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>75,35; 78,49</t>
+          <t>75,25; 78,3</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>74,27; 82,34</t>
+          <t>73,92; 77,04</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>74,42; 77,33</t>
+          <t>74,35; 77,32</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>65,63; 69,03</t>
+          <t>65,73; 69,16</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>69,9; 73,04</t>
+          <t>69,91; 73,02</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>53,22; 70,55</t>
+          <t>67,72; 70,57</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>77,61; 79,61</t>
+          <t>77,7; 79,68</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>69,68; 71,95</t>
+          <t>69,55; 71,73</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>72,94; 75,15</t>
+          <t>72,96; 75,19</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>64,36; 74,58</t>
+          <t>71,3; 73,35</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>337835</t>
+          <t>350085</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>260133</t>
+          <t>296578</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>597969</t>
+          <t>646662</t>
         </is>
       </c>
     </row>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>422614; 450755</t>
+          <t>420941; 449821</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>363861; 394596</t>
+          <t>365825; 395051</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>334356; 365505</t>
+          <t>333228; 364959</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311555; 354753</t>
+          <t>328334; 366002</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>393859; 421215</t>
+          <t>393552; 419893</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>311699; 348086</t>
+          <t>313118; 348537</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>304005; 335401</t>
+          <t>304286; 335696</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>241732; 274793</t>
+          <t>276158; 313808</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>825652; 863724</t>
+          <t>823882; 863346</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>687494; 735656</t>
+          <t>689718; 733939</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>650060; 693758</t>
+          <t>649218; 691033</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>567977; 620733</t>
+          <t>619104; 671608</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>342922</t>
+          <t>393448</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>411731</t>
+          <t>392715</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>754654</t>
+          <t>786163</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>618367; 656484</t>
+          <t>619817; 655791</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>530684; 574067</t>
+          <t>531288; 572211</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>465576; 504373</t>
+          <t>465640; 503871</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>322841; 360768</t>
+          <t>372355; 410222</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>506296; 543707</t>
+          <t>507364; 541870</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>461622; 502185</t>
+          <t>461579; 502435</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>458181; 491238</t>
+          <t>456531; 490379</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>386558; 448141</t>
+          <t>371933; 410114</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1134480; 1188507</t>
+          <t>1136314; 1187423</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1006439; 1065673</t>
+          <t>997614; 1062469</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>934236; 985284</t>
+          <t>934327; 984950</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>724802; 790211</t>
+          <t>753155; 810339</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>416628</t>
+          <t>486038</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>401150</t>
+          <t>458004</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>817778</t>
+          <t>944041</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>505689; 543117</t>
+          <t>503873; 541623</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>510735; 555102</t>
+          <t>509564; 556996</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>513782; 557587</t>
+          <t>516528; 557284</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>398799; 436558</t>
+          <t>463928; 505194</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>550203; 589965</t>
+          <t>550794; 591270</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>524042; 571482</t>
+          <t>522278; 569943</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>499987; 541563</t>
+          <t>502465; 542724</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>384634; 415708</t>
+          <t>440074; 474838</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1064975; 1121526</t>
+          <t>1068479; 1121019</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1050754; 1112250</t>
+          <t>1050507; 1112749</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1028403; 1086583</t>
+          <t>1029523; 1088755</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>791464; 840203</t>
+          <t>916099; 971283</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>694979</t>
+          <t>494555</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>509880</t>
+          <t>516585</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1204858</t>
+          <t>1011140</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>403639; 440740</t>
+          <t>405251; 441636</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>425871; 471898</t>
+          <t>426224; 474162</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>488161; 532531</t>
+          <t>487451; 530252</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>613099; 788956</t>
+          <t>467748; 518999</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>385168; 421072</t>
+          <t>384068; 422905</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>386336; 437672</t>
+          <t>386761; 436030</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>444006; 489949</t>
+          <t>445246; 492462</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>488926; 542136</t>
+          <t>497836; 534361</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>799852; 853283</t>
+          <t>800246; 854823</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>826755; 895361</t>
+          <t>825771; 894644</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>944499; 1011672</t>
+          <t>944442; 1008427</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1122736; 1357326</t>
+          <t>980101; 1045135</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>387837</t>
+          <t>421482</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>321948</t>
+          <t>360415</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>709785</t>
+          <t>781896</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>283958; 315716</t>
+          <t>284094; 315101</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>294484; 331895</t>
+          <t>294838; 333286</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>336579; 377577</t>
+          <t>338699; 378997</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>364516; 406708</t>
+          <t>399423; 441133</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>275733; 308913</t>
+          <t>276913; 310156</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>241050; 285157</t>
+          <t>240492; 284932</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>300060; 343744</t>
+          <t>300586; 344455</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>306259; 338506</t>
+          <t>342847; 378524</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>570188; 617470</t>
+          <t>571951; 617927</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>547028; 603289</t>
+          <t>548364; 605501</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>654130; 714186</t>
+          <t>652936; 713586</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>681002; 733836</t>
+          <t>753193; 811455</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>236808</t>
+          <t>260761</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>234498</t>
+          <t>256824</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>471305</t>
+          <t>517585</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>169489; 202284</t>
+          <t>169186; 200821</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>148467; 186496</t>
+          <t>149911; 186780</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>193858; 229593</t>
+          <t>193725; 229582</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>222630; 250919</t>
+          <t>245367; 276132</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>174179; 207936</t>
+          <t>174506; 208938</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>169285; 205703</t>
+          <t>172194; 207289</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>178822; 219273</t>
+          <t>179435; 218552</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>97401; 362905</t>
+          <t>241736; 270126</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>354276; 401748</t>
+          <t>355607; 402923</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>329422; 383032</t>
+          <t>328963; 381427</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>383930; 435854</t>
+          <t>385220; 437957</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>229538; 606624</t>
+          <t>496088; 537645</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>165169</t>
+          <t>181870</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>208114</t>
+          <t>229408</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>373283</t>
+          <t>411279</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>106453; 133388</t>
+          <t>104846; 132404</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>113307; 146950</t>
+          <t>112762; 146378</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>131126; 160204</t>
+          <t>132291; 160995</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>151020; 177909</t>
+          <t>168745; 195380</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>135407; 174910</t>
+          <t>134567; 174617</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>147535; 186585</t>
+          <t>149590; 188792</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>190540; 234184</t>
+          <t>189663; 235958</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>193897; 222548</t>
+          <t>213903; 244558</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>251270; 299894</t>
+          <t>248718; 297676</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>274114; 323152</t>
+          <t>271248; 326272</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>333382; 388199</t>
+          <t>332500; 384809</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>354158; 391495</t>
+          <t>391145; 431142</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2582177</t>
+          <t>2588239</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>2347455</t>
+          <t>2510528</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>4929632</t>
+          <t>5098767</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>2582930; 2674378</t>
+          <t>2579842; 2675558</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2471615; 2581173</t>
+          <t>2478624; 2587028</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2552675; 2658807</t>
+          <t>2549311; 2652481</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2493003; 2764034</t>
+          <t>2534456; 2641203</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>2498276; 2596209</t>
+          <t>2496057; 2595772</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2329295; 2449801</t>
+          <t>2332575; 2454347</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2467351; 2578401</t>
+          <t>2467735; 2577470</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>1893941; 2510660</t>
+          <t>2453912; 2557005</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>5112156; 5243770</t>
+          <t>5117800; 5248057</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>4851463; 5009745</t>
+          <t>4842440; 4994265</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>5045986; 5198786</t>
+          <t>5046798; 5201128</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>4450941; 5157772</t>
+          <t>5028185; 5172690</t>
         </is>
       </c>
     </row>
